--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108664</v>
+        <v>108676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108676</v>
+        <v>108677</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108677</v>
+        <v>108682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108682</v>
+        <v>108686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108686</v>
+        <v>108688</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108688</v>
+        <v>108698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108698</v>
+        <v>108702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108702</v>
+        <v>108705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108705</v>
+        <v>108706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108706</v>
+        <v>108723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32845-2023 artfynd.xlsx
+++ b/artfynd/A 32845-2023 artfynd.xlsx
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3067488</v>
+        <v>66538258</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granliden, 500 m SÖ om, Vrm</t>
+          <t>Saknar namn, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>377000.4744025131</v>
+        <v>377076</v>
       </c>
       <c r="R2" t="n">
-        <v>6613453.162083929</v>
+        <v>6613479</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-11-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-11-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>665 bladrosetter med 31 fröställningar, mittkoordinat, spridd från 249-507 åt öster till 246-613, 30 rosetter även vid 190-719</t>
+          <t>2012-05-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,84 +757,65 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre granskog med inslag av tallar, rikligt med blåsippor i västra delen</t>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>21091</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1325798</v>
+        <v>66538259</v>
       </c>
       <c r="B3" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4786</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius volemus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granliden, 500 m SÖ om, Vrm</t>
+          <t>Saknar namn, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377000.4744025131</v>
+        <v>377023</v>
       </c>
       <c r="R3" t="n">
-        <v>6613453.162083929</v>
+        <v>6613447</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -890,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-11-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-11-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,25 +859,20 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre granskog med inslag av tallar, rikligt med blåsippor i västra delen</t>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>21092</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -945,12 +882,7 @@
         <v>1277908</v>
       </c>
       <c r="B4" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377000.4744025131</v>
+        <v>377000</v>
       </c>
       <c r="R4" t="n">
-        <v>6613453.162083929</v>
+        <v>6613453</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1024,19 +956,9 @@
           <t>2012-11-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-11-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1078,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66538264</v>
+        <v>66538261</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1118,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376927.5658911498</v>
+        <v>376917</v>
       </c>
       <c r="R5" t="n">
-        <v>6613424.695026184</v>
+        <v>6613455</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1151,21 +1068,11 @@
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1177,7 +1084,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,50 +1102,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66538259</v>
+        <v>1325798</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4786</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Saknar namn, Vrm</t>
+          <t>Granliden, 500 m SÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377022.5687943129</v>
+        <v>377000</v>
       </c>
       <c r="R6" t="n">
-        <v>6613446.870085502</v>
+        <v>6613453</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1265,22 +1176,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-11-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-11-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,57 +1193,57 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>21092</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>äldre granskog med inslag av tallar, rikligt med blåsippor i västra delen</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66538258</v>
+        <v>66538264</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1352,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377075.8135917631</v>
+        <v>376928</v>
       </c>
       <c r="R7" t="n">
-        <v>6613478.514577369</v>
+        <v>6613425</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1385,21 +1286,11 @@
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1411,7 +1302,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1429,37 +1320,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66538261</v>
+        <v>66538262</v>
       </c>
       <c r="B8" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>6020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1469,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376917.4248567347</v>
+        <v>376917</v>
       </c>
       <c r="R8" t="n">
-        <v>6613455.387241877</v>
+        <v>6613455</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1502,21 +1388,11 @@
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1528,7 +1404,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>21094</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1546,50 +1422,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66538262</v>
+        <v>3067488</v>
       </c>
       <c r="B9" t="n">
-        <v>89233</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6020</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Saknar namn, Vrm</t>
+          <t>Granliden, 500 m SÖ om, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376917.4248567347</v>
+        <v>377000</v>
       </c>
       <c r="R9" t="n">
-        <v>6613455.387241877</v>
+        <v>6613453</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1616,22 +1496,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-11-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>665 bladrosetter med 31 fröställningar, mittkoordinat, spridd från 249-507 åt öster till 246-613, 30 rosetter även vid 190-719</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,20 +1518,25 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>21095</t>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre granskog med inslag av tallar, rikligt med blåsippor i västra delen</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Per Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1666,7 +1546,7 @@
         <v>129676316</v>
       </c>
       <c r="B10" t="n">
-        <v>108723</v>
+        <v>109105</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
